--- a/reports/gms_6_20260320.xlsx
+++ b/reports/gms_6_20260320.xlsx
@@ -2663,7 +2663,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>513.00</t>
+          <t>508.00</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>-6.81%</t>
+          <t>-0.97%</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>55.85</t>
+          <t>59.50</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2772,7 +2772,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>-0.71%</t>
+          <t>6.54%</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
